--- a/docs/02_基本設計/04_API・外部IF/KF-BD-011_API一覧.xlsx
+++ b/docs/02_基本設計/04_API・外部IF/KF-BD-011_API一覧.xlsx
@@ -600,7 +600,7 @@
       </c>
       <c r="C10" s="3" t="inlineStr">
         <is>
-          <t>1.2</t>
+          <t>1.3</t>
         </is>
       </c>
       <c r="D10" s="10" t="n"/>
@@ -631,6 +631,8 @@
       </c>
       <c r="D12" s="10" t="n"/>
     </row>
+    <row r="13"/>
+    <row r="14"/>
     <row r="15">
       <c r="D15" s="5" t="inlineStr">
         <is>
@@ -677,7 +679,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:E4"/>
+  <dimension ref="A1:E5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -782,6 +784,29 @@
         </is>
       </c>
       <c r="E4" s="11" t="n"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="11" t="inlineStr">
+        <is>
+          <t>1.3</t>
+        </is>
+      </c>
+      <c r="B5" s="11" t="inlineStr">
+        <is>
+          <t>2026/10/04</t>
+        </is>
+      </c>
+      <c r="C5" s="11" t="inlineStr">
+        <is>
+          <t>Wang Sheng</t>
+        </is>
+      </c>
+      <c r="D5" s="11" t="inlineStr">
+        <is>
+          <t>API-023（パスワード変更）を追加。API-001 の概要にトークン有効 2 時間・ロック・mustChangePassword を追記</t>
+        </is>
+      </c>
+      <c r="E5" s="11" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -795,7 +820,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:G25"/>
+  <dimension ref="A1:G26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -814,6 +839,7 @@
         </is>
       </c>
     </row>
+    <row r="2"/>
     <row r="3">
       <c r="A3" s="7" t="inlineStr">
         <is>
@@ -874,7 +900,7 @@
       </c>
       <c r="E4" s="8" t="inlineStr">
         <is>
-          <t>認証してトークンを発行</t>
+          <t>認証してトークンを発行（有効 2 時間）。5 回連続失敗で 30 分ロック（423）。初期パスワードの利用者には mustChangePassword=true を返す</t>
         </is>
       </c>
       <c r="F4" s="8" t="inlineStr">
@@ -1662,6 +1688,43 @@
       <c r="G25" s="11" t="inlineStr">
         <is>
           <t>F-03, F-04, F-05</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="11" t="inlineStr">
+        <is>
+          <t>API-023</t>
+        </is>
+      </c>
+      <c r="B26" s="11" t="inlineStr">
+        <is>
+          <t>パスワード変更</t>
+        </is>
+      </c>
+      <c r="C26" s="11" t="inlineStr">
+        <is>
+          <t>POST</t>
+        </is>
+      </c>
+      <c r="D26" s="11" t="inlineStr">
+        <is>
+          <t>/api/auth/password</t>
+        </is>
+      </c>
+      <c r="E26" s="11" t="inlineStr">
+        <is>
+          <t>ログイン中の本人のパスワードを変更（成功時 204。現在のパスワードの照合とポリシー検査を行う）</t>
+        </is>
+      </c>
+      <c r="F26" s="11" t="inlineStr">
+        <is>
+          <t>全員（本人）</t>
+        </is>
+      </c>
+      <c r="G26" s="11" t="inlineStr">
+        <is>
+          <t>F-12</t>
         </is>
       </c>
     </row>

--- a/docs/02_基本設計/04_API・外部IF/KF-BD-011_API一覧.xlsx
+++ b/docs/02_基本設計/04_API・外部IF/KF-BD-011_API一覧.xlsx
@@ -10,6 +10,8 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="表紙" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="改訂履歴" sheetId="2" state="visible" r:id="rId2"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="API一覧" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="エンドポイント一覧" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="共通仕様" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -78,7 +80,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="6">
+  <borders count="7">
     <border>
       <left/>
       <right/>
@@ -147,11 +149,17 @@
         <color rgb="00999999"/>
       </bottom>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -174,6 +182,12 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -600,7 +614,7 @@
       </c>
       <c r="C10" s="3" t="inlineStr">
         <is>
-          <t>1.3</t>
+          <t>1.5</t>
         </is>
       </c>
       <c r="D10" s="10" t="n"/>
@@ -679,7 +693,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:E5"/>
+  <dimension ref="A1:E7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -807,6 +821,52 @@
         </is>
       </c>
       <c r="E5" s="11" t="n"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="11" t="inlineStr">
+        <is>
+          <t>1.4</t>
+        </is>
+      </c>
+      <c r="B6" s="11" t="inlineStr">
+        <is>
+          <t>2026/10/05</t>
+        </is>
+      </c>
+      <c r="C6" s="11" t="inlineStr">
+        <is>
+          <t>Wang Sheng</t>
+        </is>
+      </c>
+      <c r="D6" s="11" t="inlineStr">
+        <is>
+          <t>実装（Controller / SecurityConfig / DTO）との全面照合。エンドポイント一覧・共通仕様シートを追加。API-004/010〜012（{stepId}）/014（GET /{id}・PUT /{id}/password）/015（GET /{id}）/017/018（format=json|csv・month 必須）/019（POST /{id}/read）/020（上長のみ・管理者は 403）の記述を修正し、actuator/health を追記</t>
+        </is>
+      </c>
+      <c r="E6" s="11" t="n"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="11" t="inlineStr">
+        <is>
+          <t>1.5</t>
+        </is>
+      </c>
+      <c r="B7" s="11" t="inlineStr">
+        <is>
+          <t>2026/10/05</t>
+        </is>
+      </c>
+      <c r="C7" s="11" t="inlineStr">
+        <is>
+          <t>Wang Sheng</t>
+        </is>
+      </c>
+      <c r="D7" s="11" t="inlineStr">
+        <is>
+          <t>休憩・離席の打刻 API（API-024 break-start・API-025 break-end）と部署一覧 API（API-026 GET /api/departments）を追加。API-004 の各日に breaks、API-003 に E-022 を追記。API-005 に休憩・離席修正申請（BREAK_CORRECTION：breakKind / breakStart / breakEnd）を追加し、API-007 に breakKind 等と承認履歴の SKIPPED（表示専用）、API-009 の申請種別に BREAK_CORRECTION を追記。API-014 の初期・再設定パスワードを 12〜72 文字・英字と数字を両方含む（本人変更と同じポリシー）に修正し、再設定でトークンが失効する旨を追記。共通仕様に E-020〜E-022（409）を追加。実装（DepartmentController 追加で @RestController 14 クラス）と照合</t>
+        </is>
+      </c>
+      <c r="E7" s="11" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -820,22 +880,22 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:G26"/>
+  <dimension ref="A1:G30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
     <col width="18" customWidth="1" min="2" max="2"/>
-    <col width="14" customWidth="1" min="3" max="3"/>
-    <col width="36" customWidth="1" min="4" max="4"/>
-    <col width="36" customWidth="1" min="5" max="5"/>
-    <col width="22" customWidth="1" min="6" max="6"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
+    <col width="40" customWidth="1" min="4" max="4"/>
+    <col width="60" customWidth="1" min="5" max="5"/>
+    <col width="26" customWidth="1" min="6" max="6"/>
     <col width="12" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="9" t="inlineStr">
         <is>
-          <t>※リクエスト・レスポンスの詳細は詳細設計で定義する。認証後はトークンを用い、各APIでロールとデータ所有を検証する。</t>
+          <t>※実装（Controller / SecurityConfig）に合わせて 2026/10/05 に全面照合。エンドポイント単位の一覧・リクエスト・レスポンス・エラーは「エンドポイント一覧」「共通仕様」シートを参照。詳細は詳細設計（KF-DD-ONL-xxx）で定義する。</t>
         </is>
       </c>
     </row>
@@ -900,17 +960,17 @@
       </c>
       <c r="E4" s="8" t="inlineStr">
         <is>
-          <t>認証してトークンを発行（有効 2 時間）。5 回連続失敗で 30 分ロック（423）。初期パスワードの利用者には mustChangePassword=true を返す</t>
+          <t>メールアドレス（前後空白除去・小文字化）とパスワードで認証し、トークンを発行（有効 2 時間）。5 回連続失敗で 30 分ロック（E-017 / HTTP 423）。初期パスワード・管理者再設定直後の利用者には mustChangePassword=true を返す</t>
         </is>
       </c>
       <c r="F4" s="8" t="inlineStr">
         <is>
-          <t>全員</t>
+          <t>全員（未認証可）</t>
         </is>
       </c>
       <c r="G4" s="8" t="inlineStr">
         <is>
-          <t>F-01</t>
+          <t>F-01, F-13</t>
         </is>
       </c>
     </row>
@@ -937,12 +997,12 @@
       </c>
       <c r="E5" s="8" t="inlineStr">
         <is>
-          <t>出勤を記録</t>
+          <t>本日（JST）の出勤をサーバー時刻で記録（成功時 201）。二重打刻は E-006</t>
         </is>
       </c>
       <c r="F5" s="8" t="inlineStr">
         <is>
-          <t>全員</t>
+          <t>全員（本人）</t>
         </is>
       </c>
       <c r="G5" s="8" t="inlineStr">
@@ -974,12 +1034,12 @@
       </c>
       <c r="E6" s="8" t="inlineStr">
         <is>
-          <t>退勤を記録</t>
+          <t>本日の退勤を記録し、休憩・離席の打刻を反映した勤務時間・残業時間（分）を計算して保存。休憩中・離席中は退勤できない（E-022）</t>
         </is>
       </c>
       <c r="F6" s="8" t="inlineStr">
         <is>
-          <t>全員</t>
+          <t>全員（本人）</t>
         </is>
       </c>
       <c r="G6" s="8" t="inlineStr">
@@ -1006,17 +1066,17 @@
       </c>
       <c r="D7" s="8" t="inlineStr">
         <is>
-          <t>/api/attendance?month=</t>
+          <t>/api/attendance?month=yyyy-MM</t>
         </is>
       </c>
       <c r="E7" s="8" t="inlineStr">
         <is>
-          <t>自分の月次勤怠を取得</t>
+          <t>自分の月次勤怠（日別明細と月合計）を取得。各日に休憩・離席の区間（breaks）を含む。month は必須（未来月は不可）</t>
         </is>
       </c>
       <c r="F7" s="8" t="inlineStr">
         <is>
-          <t>全員</t>
+          <t>全員（本人）</t>
         </is>
       </c>
       <c r="G7" s="8" t="inlineStr">
@@ -1048,12 +1108,12 @@
       </c>
       <c r="E8" s="8" t="inlineStr">
         <is>
-          <t>休暇申請・打刻修正申請を提出（下書き保存も可）</t>
+          <t>休暇申請（LEAVE）・打刻修正申請（CLOCK_CORRECTION）・休憩・離席修正申請（BREAK_CORRECTION。種別・開始・終了を指定）を作成。asDraft=false（既定）で提出（承認フロー開始）、true で下書き保存（成功時 201）</t>
         </is>
       </c>
       <c r="F8" s="8" t="inlineStr">
         <is>
-          <t>全員</t>
+          <t>全員（本人）</t>
         </is>
       </c>
       <c r="G8" s="8" t="inlineStr">
@@ -1080,17 +1140,17 @@
       </c>
       <c r="D9" s="8" t="inlineStr">
         <is>
-          <t>/api/requests</t>
+          <t>/api/requests[?status=]</t>
         </is>
       </c>
       <c r="E9" s="8" t="inlineStr">
         <is>
-          <t>自分の申請一覧を取得</t>
+          <t>自分の申請一覧（下書き含む）を取得。管理者も自分の申請のみ。status で絞込</t>
         </is>
       </c>
       <c r="F9" s="8" t="inlineStr">
         <is>
-          <t>全員</t>
+          <t>全員（本人）</t>
         </is>
       </c>
       <c r="G9" s="8" t="inlineStr">
@@ -1122,17 +1182,17 @@
       </c>
       <c r="E10" s="8" t="inlineStr">
         <is>
-          <t>申請の詳細と承認履歴を取得</t>
+          <t>申請の詳細・承認履歴・申請者の休暇残日数を取得。承認履歴の段の状態は、取下げ・差戻し・却下で打ち切られた未処理の段を SKIPPED（処理なし。表示専用で DB には保存しない）として返す。申請者と承認者の画面で共用</t>
         </is>
       </c>
       <c r="F10" s="8" t="inlineStr">
         <is>
-          <t>全員（本人・承認者）</t>
+          <t>全員（本人・承認ステップの承認者・管理者。下書きは本人のみ）</t>
         </is>
       </c>
       <c r="G10" s="8" t="inlineStr">
         <is>
-          <t>F-05</t>
+          <t>F-05, F-06</t>
         </is>
       </c>
     </row>
@@ -1159,7 +1219,7 @@
       </c>
       <c r="E11" s="8" t="inlineStr">
         <is>
-          <t>承認前の申請を取り下げ</t>
+          <t>承認前（下書き・承認待ち・差戻し）の申請を取り下げ。承認待ちの取下げは現在の承認者へ通知</t>
         </is>
       </c>
       <c r="F11" s="8" t="inlineStr">
@@ -1191,12 +1251,12 @@
       </c>
       <c r="D12" s="8" t="inlineStr">
         <is>
-          <t>/api/approvals/pending</t>
+          <t>/api/approvals/pending[?requestType=&amp;stepNo=]</t>
         </is>
       </c>
       <c r="E12" s="8" t="inlineStr">
         <is>
-          <t>自分が承認する申請を取得</t>
+          <t>自分が今処理できる承認ステップを取得（上長＝自分が 1 段目に指名された申請、管理者＝自分宛の 1 段目＋全員分の 2 段目）。提出日の古い順。申請種別（requestType）は LEAVE / CLOCK_CORRECTION / BREAK_CORRECTION</t>
         </is>
       </c>
       <c r="F12" s="8" t="inlineStr">
@@ -1228,12 +1288,12 @@
       </c>
       <c r="D13" s="8" t="inlineStr">
         <is>
-          <t>/api/approvals/{id}/approve</t>
+          <t>/api/approvals/{stepId}/approve</t>
         </is>
       </c>
       <c r="E13" s="8" t="inlineStr">
         <is>
-          <t>承認処理（コメント任意）</t>
+          <t>承認処理（コメント任意・本文省略可）。{stepId} は API-009 の items[].stepId（申請 ID ではない）。1 段目は 2 段目へ進め、2 段目は申請を確定して残日数消化／打刻反映（休憩・離席修正は区間を追加・修正して勤務時間を再計算）</t>
         </is>
       </c>
       <c r="F13" s="8" t="inlineStr">
@@ -1265,12 +1325,12 @@
       </c>
       <c r="D14" s="8" t="inlineStr">
         <is>
-          <t>/api/approvals/{id}/return</t>
+          <t>/api/approvals/{stepId}/return</t>
         </is>
       </c>
       <c r="E14" s="8" t="inlineStr">
         <is>
-          <t>差戻し処理（コメント必須）</t>
+          <t>差戻し処理（コメント必須）。{stepId} は承認ステップ ID</t>
         </is>
       </c>
       <c r="F14" s="8" t="inlineStr">
@@ -1302,12 +1362,12 @@
       </c>
       <c r="D15" s="8" t="inlineStr">
         <is>
-          <t>/api/approvals/{id}/reject</t>
+          <t>/api/approvals/{stepId}/reject</t>
         </is>
       </c>
       <c r="E15" s="8" t="inlineStr">
         <is>
-          <t>却下処理（コメント必須）</t>
+          <t>却下処理（コメント必須）。{stepId} は承認ステップ ID</t>
         </is>
       </c>
       <c r="F15" s="8" t="inlineStr">
@@ -1344,12 +1404,12 @@
       </c>
       <c r="E16" s="8" t="inlineStr">
         <is>
-          <t>自分の休暇残日数を取得</t>
+          <t>自分の休暇残日数（種別別・付与行別）、年 5 日取得義務の進捗、次回付与予定日を取得</t>
         </is>
       </c>
       <c r="F16" s="8" t="inlineStr">
         <is>
-          <t>全員</t>
+          <t>全員（本人）</t>
         </is>
       </c>
       <c r="G16" s="8" t="inlineStr">
@@ -1376,12 +1436,12 @@
       </c>
       <c r="D17" s="8" t="inlineStr">
         <is>
-          <t>/api/admin/users</t>
+          <t>/api/admin/users［/{id}］［/{id}/password］</t>
         </is>
       </c>
       <c r="E17" s="8" t="inlineStr">
         <is>
-          <t>ユーザーの登録・変更・無効化</t>
+          <t>一覧・詳細取得（GET）、登録（POST）、変更・無効化（PUT /{id}）、パスワード再設定（PUT /{id}/password。設定後は要変更・ロック解除・以前に発行されたトークンは失効）。初期・再設定パスワードは本人変更と同じポリシー（12〜72 文字・半角の英字と数字を両方含む）。物理削除はしない</t>
         </is>
       </c>
       <c r="F17" s="8" t="inlineStr">
@@ -1413,12 +1473,12 @@
       </c>
       <c r="D18" s="8" t="inlineStr">
         <is>
-          <t>/api/admin/leave-types</t>
+          <t>/api/admin/leave-types［/{id}］</t>
         </is>
       </c>
       <c r="E18" s="8" t="inlineStr">
         <is>
-          <t>休暇種別の管理</t>
+          <t>休暇種別の一覧（activeOnly 指定可）・詳細・登録・変更。年次有給休暇の名称・有給区分・日数ルール・有効フラグは変更不可（E-016）</t>
         </is>
       </c>
       <c r="F18" s="8" t="inlineStr">
@@ -1450,12 +1510,12 @@
       </c>
       <c r="D19" s="8" t="inlineStr">
         <is>
-          <t>/api/admin/holidays</t>
+          <t>/api/admin/holidays［/{id}］</t>
         </is>
       </c>
       <c r="E19" s="8" t="inlineStr">
         <is>
-          <t>祝日・会社休日の管理</t>
+          <t>祝日・会社休日の一覧（year 指定。省略時は本年）・登録・削除（マスタのため物理削除）</t>
         </is>
       </c>
       <c r="F19" s="8" t="inlineStr">
@@ -1482,17 +1542,17 @@
       </c>
       <c r="C20" s="8" t="inlineStr">
         <is>
-          <t>GET/POST/PUT</t>
+          <t>GET / POST / PUT</t>
         </is>
       </c>
       <c r="D20" s="8" t="inlineStr">
         <is>
-          <t>/api/admin/leave-grants</t>
+          <t>/api/admin/leave-grants［/{id}］</t>
         </is>
       </c>
       <c r="E20" s="8" t="inlineStr">
         <is>
-          <t>年次有給休暇の付与・調整</t>
+          <t>付与履歴の参照（userId 必須）・手動付与の追加（POST）・付与日数の調整（PUT /{id}）。付与・調整時は本人へ通知</t>
         </is>
       </c>
       <c r="F20" s="8" t="inlineStr">
@@ -1524,12 +1584,12 @@
       </c>
       <c r="D21" s="8" t="inlineStr">
         <is>
-          <t>/api/admin/reports/monthly</t>
+          <t>/api/admin/reports/monthly?month=yyyy-MM[&amp;departmentId=][&amp;format=json|csv]</t>
         </is>
       </c>
       <c r="E21" s="8" t="inlineStr">
         <is>
-          <t>月次集計とCSV出力</t>
+          <t>全社（部署絞込可）の月次集計。format=json（既定）で JSON、csv で RPT-001 を UTF-8 BOM 付き CSV でダウンロード（kintai_summary_yyyyMM.csv）。month は必須</t>
         </is>
       </c>
       <c r="F21" s="8" t="inlineStr">
@@ -1551,7 +1611,7 @@
       </c>
       <c r="B22" s="8" t="inlineStr">
         <is>
-          <t>通知一覧取得</t>
+          <t>通知一覧取得・既読化</t>
         </is>
       </c>
       <c r="C22" s="8" t="inlineStr">
@@ -1561,17 +1621,17 @@
       </c>
       <c r="D22" s="8" t="inlineStr">
         <is>
-          <t>/api/notifications</t>
+          <t>/api/notifications［/{id}/read］</t>
         </is>
       </c>
       <c r="E22" s="8" t="inlineStr">
         <is>
-          <t>自分の通知を取得</t>
+          <t>自分の通知を新しい順に最大 50 件取得（GET）。通知 1 件を既読化（POST /{id}/read。冪等。他人の通知は E-010）</t>
         </is>
       </c>
       <c r="F22" s="8" t="inlineStr">
         <is>
-          <t>全員</t>
+          <t>全員（本人）</t>
         </is>
       </c>
       <c r="G22" s="8" t="inlineStr">
@@ -1598,17 +1658,17 @@
       </c>
       <c r="D23" s="8" t="inlineStr">
         <is>
-          <t>/api/manager/subordinates/summary</t>
+          <t>/api/manager/subordinates/summary?month=yyyy-MM</t>
         </is>
       </c>
       <c r="E23" s="8" t="inlineStr">
         <is>
-          <t>上長が部下の月次集計を取得</t>
+          <t>上長が直属の部下の月次集計を取得。上長 ID は JWT から決定。month は必須</t>
         </is>
       </c>
       <c r="F23" s="8" t="inlineStr">
         <is>
-          <t>上長</t>
+          <t>上長のみ（管理者・従業員は 403）</t>
         </is>
       </c>
       <c r="G23" s="8" t="inlineStr">
@@ -1618,113 +1678,261 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="11" t="inlineStr">
+      <c r="A24" s="8" t="inlineStr">
         <is>
           <t>API-021</t>
         </is>
       </c>
-      <c r="B24" s="11" t="inlineStr">
+      <c r="B24" s="8" t="inlineStr">
         <is>
           <t>有効休暇種別一覧取得</t>
         </is>
       </c>
-      <c r="C24" s="11" t="inlineStr">
+      <c r="C24" s="8" t="inlineStr">
         <is>
           <t>GET</t>
         </is>
       </c>
-      <c r="D24" s="11" t="inlineStr">
+      <c r="D24" s="8" t="inlineStr">
         <is>
           <t>/api/leave-types</t>
         </is>
       </c>
-      <c r="E24" s="11" t="inlineStr">
-        <is>
-          <t>申請画面の休暇種別プルダウン用に有効な休暇種別を取得</t>
-        </is>
-      </c>
-      <c r="F24" s="11" t="inlineStr">
+      <c r="E24" s="8" t="inlineStr">
+        <is>
+          <t>申請画面の休暇種別プルダウン用に有効な休暇種別を取得（5 項目）</t>
+        </is>
+      </c>
+      <c r="F24" s="8" t="inlineStr">
         <is>
           <t>全員</t>
         </is>
       </c>
-      <c r="G24" s="11" t="inlineStr">
+      <c r="G24" s="8" t="inlineStr">
         <is>
           <t>F-04</t>
         </is>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="11" t="inlineStr">
+      <c r="A25" s="8" t="inlineStr">
         <is>
           <t>API-022</t>
         </is>
       </c>
-      <c r="B25" s="11" t="inlineStr">
+      <c r="B25" s="8" t="inlineStr">
         <is>
           <t>申請提出</t>
         </is>
       </c>
-      <c r="C25" s="11" t="inlineStr">
+      <c r="C25" s="8" t="inlineStr">
         <is>
           <t>POST</t>
         </is>
       </c>
-      <c r="D25" s="11" t="inlineStr">
+      <c r="D25" s="8" t="inlineStr">
         <is>
           <t>/api/requests/{id}/submit</t>
         </is>
       </c>
-      <c r="E25" s="11" t="inlineStr">
-        <is>
-          <t>下書き・差戻しの申請を提出（再提出）</t>
-        </is>
-      </c>
-      <c r="F25" s="11" t="inlineStr">
+      <c r="E25" s="8" t="inlineStr">
+        <is>
+          <t>下書き・差戻しの申請を提出（再提出）。承認ルートを作り直す</t>
+        </is>
+      </c>
+      <c r="F25" s="8" t="inlineStr">
         <is>
           <t>全員（本人）</t>
         </is>
       </c>
-      <c r="G25" s="11" t="inlineStr">
+      <c r="G25" s="8" t="inlineStr">
         <is>
           <t>F-03, F-04, F-05</t>
         </is>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="11" t="inlineStr">
+      <c r="A26" s="8" t="inlineStr">
         <is>
           <t>API-023</t>
         </is>
       </c>
-      <c r="B26" s="11" t="inlineStr">
+      <c r="B26" s="8" t="inlineStr">
         <is>
           <t>パスワード変更</t>
         </is>
       </c>
-      <c r="C26" s="11" t="inlineStr">
+      <c r="C26" s="8" t="inlineStr">
         <is>
           <t>POST</t>
         </is>
       </c>
-      <c r="D26" s="11" t="inlineStr">
+      <c r="D26" s="8" t="inlineStr">
         <is>
           <t>/api/auth/password</t>
         </is>
       </c>
-      <c r="E26" s="11" t="inlineStr">
-        <is>
-          <t>ログイン中の本人のパスワードを変更（成功時 204。現在のパスワードの照合とポリシー検査を行う）</t>
-        </is>
-      </c>
-      <c r="F26" s="11" t="inlineStr">
+      <c r="E26" s="8" t="inlineStr">
+        <is>
+          <t>ログイン中の本人のパスワードを変更（成功時 204）。現在のパスワードの照合（誤りは失敗回数に加算）とポリシー検査を行う。要パスワード変更（mustChangePassword）のトークンでも呼べる唯一の API</t>
+        </is>
+      </c>
+      <c r="F26" s="8" t="inlineStr">
         <is>
           <t>全員（本人）</t>
         </is>
       </c>
-      <c r="G26" s="11" t="inlineStr">
+      <c r="G26" s="8" t="inlineStr">
         <is>
           <t>F-12</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="8" t="inlineStr">
+        <is>
+          <t>API-024</t>
+        </is>
+      </c>
+      <c r="B27" s="8" t="inlineStr">
+        <is>
+          <t>休憩・離席の開始</t>
+        </is>
+      </c>
+      <c r="C27" s="8" t="inlineStr">
+        <is>
+          <t>POST</t>
+        </is>
+      </c>
+      <c r="D27" s="8" t="inlineStr">
+        <is>
+          <t>/api/attendance/break-start</t>
+        </is>
+      </c>
+      <c r="E27" s="8" t="inlineStr">
+        <is>
+          <t>本日の休憩（BREAK）または日中離席（AWAY）の開始をサーバー時刻で記録（成功時 201）。本文は種別（kind）のみ。開始中の区間が既にあれば E-020、出勤打刻がなければ E-007、退勤済みなら E-006（409）。応答は本日の状態（開始中の種別と区間一覧）</t>
+        </is>
+      </c>
+      <c r="F27" s="8" t="inlineStr">
+        <is>
+          <t>全員（本人）</t>
+        </is>
+      </c>
+      <c r="G27" s="8" t="inlineStr">
+        <is>
+          <t>F-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="8" t="inlineStr">
+        <is>
+          <t>API-025</t>
+        </is>
+      </c>
+      <c r="B28" s="8" t="inlineStr">
+        <is>
+          <t>休憩・離席の終了</t>
+        </is>
+      </c>
+      <c r="C28" s="8" t="inlineStr">
+        <is>
+          <t>POST</t>
+        </is>
+      </c>
+      <c r="D28" s="8" t="inlineStr">
+        <is>
+          <t>/api/attendance/break-end</t>
+        </is>
+      </c>
+      <c r="E28" s="8" t="inlineStr">
+        <is>
+          <t>開始中の休憩・離席を終了する（200）。本文なし。開始中の区間がなければ E-021、出勤打刻がなければ E-007、退勤済みなら E-006（409）。応答は API-024 と同じ。区間の取消・削除は未実装（修正は休憩・離席修正申請）</t>
+        </is>
+      </c>
+      <c r="F28" s="8" t="inlineStr">
+        <is>
+          <t>全員（本人）</t>
+        </is>
+      </c>
+      <c r="G28" s="8" t="inlineStr">
+        <is>
+          <t>F-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="8" t="inlineStr">
+        <is>
+          <t>API-026</t>
+        </is>
+      </c>
+      <c r="B29" s="8" t="inlineStr">
+        <is>
+          <t>部署一覧取得</t>
+        </is>
+      </c>
+      <c r="C29" s="8" t="inlineStr">
+        <is>
+          <t>GET</t>
+        </is>
+      </c>
+      <c r="D29" s="8" t="inlineStr">
+        <is>
+          <t>/api/departments</t>
+        </is>
+      </c>
+      <c r="E29" s="8" t="inlineStr">
+        <is>
+          <t>部署の一覧（id 昇順）を取得。ユーザー管理・月次集計の部署プルダウン用。ロールによる制限なし（認証必須）</t>
+        </is>
+      </c>
+      <c r="F29" s="8" t="inlineStr">
+        <is>
+          <t>全員</t>
+        </is>
+      </c>
+      <c r="G29" s="8" t="inlineStr">
+        <is>
+          <t>F-08, F-10</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="8" t="inlineStr">
+        <is>
+          <t>（API ID なし）</t>
+        </is>
+      </c>
+      <c r="B30" s="8" t="inlineStr">
+        <is>
+          <t>ヘルスチェック</t>
+        </is>
+      </c>
+      <c r="C30" s="8" t="inlineStr">
+        <is>
+          <t>GET</t>
+        </is>
+      </c>
+      <c r="D30" s="8" t="inlineStr">
+        <is>
+          <t>/actuator/health</t>
+        </is>
+      </c>
+      <c r="E30" s="8" t="inlineStr">
+        <is>
+          <t>アプリケーションの稼働確認（Spring Boot Actuator。認証不要。health のみ公開）</t>
+        </is>
+      </c>
+      <c r="F30" s="8" t="inlineStr">
+        <is>
+          <t>全員（未認証可）</t>
+        </is>
+      </c>
+      <c r="G30" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
     </row>
@@ -1732,4 +1940,1979 @@
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:I42"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="5" customWidth="1" min="1" max="1"/>
+    <col width="10" customWidth="1" min="2" max="2"/>
+    <col width="9" customWidth="1" min="3" max="3"/>
+    <col width="34" customWidth="1" min="4" max="4"/>
+    <col width="36" customWidth="1" min="5" max="5"/>
+    <col width="44" customWidth="1" min="6" max="6"/>
+    <col width="60" customWidth="1" min="7" max="7"/>
+    <col width="48" customWidth="1" min="8" max="8"/>
+    <col width="32" customWidth="1" min="9" max="9"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="9" t="inlineStr">
+        <is>
+          <t>※実装済みの全エンドポイント（@RestController 14 クラス）。日付は yyyy-MM-dd、日時は +09:00 付き ISO 8601。金額・日数は小数 1 位。エラー本文の形式は「共通仕様」を参照。</t>
+        </is>
+      </c>
+    </row>
+    <row r="2"/>
+    <row r="3">
+      <c r="A3" s="12" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="B3" s="12" t="inlineStr">
+        <is>
+          <t>API-ID</t>
+        </is>
+      </c>
+      <c r="C3" s="12" t="inlineStr">
+        <is>
+          <t>メソッド</t>
+        </is>
+      </c>
+      <c r="D3" s="12" t="inlineStr">
+        <is>
+          <t>パス</t>
+        </is>
+      </c>
+      <c r="E3" s="12" t="inlineStr">
+        <is>
+          <t>認可（実装）</t>
+        </is>
+      </c>
+      <c r="F3" s="12" t="inlineStr">
+        <is>
+          <t>リクエスト（パス/クエリ/本文）</t>
+        </is>
+      </c>
+      <c r="G3" s="12" t="inlineStr">
+        <is>
+          <t>成功応答（HTTP / 本文）</t>
+        </is>
+      </c>
+      <c r="H3" s="12" t="inlineStr">
+        <is>
+          <t>主なエラー（コード / HTTP）</t>
+        </is>
+      </c>
+      <c r="I3" s="12" t="inlineStr">
+        <is>
+          <t>実装クラス#メソッド</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="B4" s="13" t="inlineStr">
+        <is>
+          <t>API-001</t>
+        </is>
+      </c>
+      <c r="C4" s="13" t="inlineStr">
+        <is>
+          <t>POST</t>
+        </is>
+      </c>
+      <c r="D4" s="13" t="inlineStr">
+        <is>
+          <t>/api/auth/login</t>
+        </is>
+      </c>
+      <c r="E4" s="13" t="inlineStr">
+        <is>
+          <t>permitAll（SecurityConfig）</t>
+        </is>
+      </c>
+      <c r="F4" s="13" t="inlineStr">
+        <is>
+          <t>本文: email（必須・255 文字以内）, password（必須）</t>
+        </is>
+      </c>
+      <c r="G4" s="13" t="inlineStr">
+        <is>
+          <t>200 / {token, userId, name, role, mustChangePassword}</t>
+        </is>
+      </c>
+      <c r="H4" s="13" t="inlineStr">
+        <is>
+          <t>E-002 / 400, E-001 / 401（不存在・無効・不一致は同一文言）, E-017 / 423（ロック中）</t>
+        </is>
+      </c>
+      <c r="I4" s="13" t="inlineStr">
+        <is>
+          <t>AuthController#login</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="13" t="n">
+        <v>2</v>
+      </c>
+      <c r="B5" s="13" t="inlineStr">
+        <is>
+          <t>API-023</t>
+        </is>
+      </c>
+      <c r="C5" s="13" t="inlineStr">
+        <is>
+          <t>POST</t>
+        </is>
+      </c>
+      <c r="D5" s="13" t="inlineStr">
+        <is>
+          <t>/api/auth/password</t>
+        </is>
+      </c>
+      <c r="E5" s="13" t="inlineStr">
+        <is>
+          <t>全ロール（認証必須）。mustChangePassword トークンも可（PasswordChangeRequiredFilter の唯一の例外）</t>
+        </is>
+      </c>
+      <c r="F5" s="13" t="inlineStr">
+        <is>
+          <t>本文: currentPassword（必須）, newPassword（必須・128 文字以内）。対象は JWT の本人のみ</t>
+        </is>
+      </c>
+      <c r="G5" s="13" t="inlineStr">
+        <is>
+          <t>204 / 本文なし</t>
+        </is>
+      </c>
+      <c r="H5" s="13" t="inlineStr">
+        <is>
+          <t>E-002 / 400（必須・ポリシー違反: 12 文字以上・半角英数字を両方含む・現在と異なる・72 バイト以内）, E-018 / 400（現在のパスワード不一致。失敗回数に加算）, E-017 / 423, E-015 / 404</t>
+        </is>
+      </c>
+      <c r="I5" s="13" t="inlineStr">
+        <is>
+          <t>AuthController#changePassword</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="13" t="n">
+        <v>3</v>
+      </c>
+      <c r="B6" s="13" t="inlineStr">
+        <is>
+          <t>API-002</t>
+        </is>
+      </c>
+      <c r="C6" s="13" t="inlineStr">
+        <is>
+          <t>POST</t>
+        </is>
+      </c>
+      <c r="D6" s="13" t="inlineStr">
+        <is>
+          <t>/api/attendance/clock-in</t>
+        </is>
+      </c>
+      <c r="E6" s="13" t="inlineStr">
+        <is>
+          <t>全ロール（認証必須）</t>
+        </is>
+      </c>
+      <c r="F6" s="13" t="inlineStr">
+        <is>
+          <t>なし（本人・本日）</t>
+        </is>
+      </c>
+      <c r="G6" s="13" t="inlineStr">
+        <is>
+          <t>201 / {workDate, clockIn}</t>
+        </is>
+      </c>
+      <c r="H6" s="13" t="inlineStr">
+        <is>
+          <t>E-006 / 409</t>
+        </is>
+      </c>
+      <c r="I6" s="13" t="inlineStr">
+        <is>
+          <t>AttendanceController#clockIn</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="13" t="n">
+        <v>4</v>
+      </c>
+      <c r="B7" s="13" t="inlineStr">
+        <is>
+          <t>API-003</t>
+        </is>
+      </c>
+      <c r="C7" s="13" t="inlineStr">
+        <is>
+          <t>POST</t>
+        </is>
+      </c>
+      <c r="D7" s="13" t="inlineStr">
+        <is>
+          <t>/api/attendance/clock-out</t>
+        </is>
+      </c>
+      <c r="E7" s="13" t="inlineStr">
+        <is>
+          <t>全ロール（認証必須）</t>
+        </is>
+      </c>
+      <c r="F7" s="13" t="inlineStr">
+        <is>
+          <t>なし（本人・本日）</t>
+        </is>
+      </c>
+      <c r="G7" s="13" t="inlineStr">
+        <is>
+          <t>200 / {clockOut, workMinutes, overtimeMinutes}</t>
+        </is>
+      </c>
+      <c r="H7" s="13" t="inlineStr">
+        <is>
+          <t>E-007 / 409（出勤打刻なし）, E-006 / 409（退勤済み）, E-022 / 409（休憩中・離席中）</t>
+        </is>
+      </c>
+      <c r="I7" s="13" t="inlineStr">
+        <is>
+          <t>AttendanceController#clockOut</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="13" t="n">
+        <v>5</v>
+      </c>
+      <c r="B8" s="13" t="inlineStr">
+        <is>
+          <t>API-024</t>
+        </is>
+      </c>
+      <c r="C8" s="13" t="inlineStr">
+        <is>
+          <t>POST</t>
+        </is>
+      </c>
+      <c r="D8" s="13" t="inlineStr">
+        <is>
+          <t>/api/attendance/break-start</t>
+        </is>
+      </c>
+      <c r="E8" s="13" t="inlineStr">
+        <is>
+          <t>全ロール（認証必須）</t>
+        </is>
+      </c>
+      <c r="F8" s="13" t="inlineStr">
+        <is>
+          <t>本文: kind（必須。BREAK|AWAY）。対象は本人・本日</t>
+        </is>
+      </c>
+      <c r="G8" s="13" t="inlineStr">
+        <is>
+          <t>201 / {workDate, openKind, breaks[{kind, startAt, endAt}]}</t>
+        </is>
+      </c>
+      <c r="H8" s="13" t="inlineStr">
+        <is>
+          <t>E-002 / 400, E-007 / 409（出勤打刻なし）, E-006 / 409（退勤済み）, E-020 / 409（既に休憩中または離席中）</t>
+        </is>
+      </c>
+      <c r="I8" s="13" t="inlineStr">
+        <is>
+          <t>AttendanceController#breakStart</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="13" t="n">
+        <v>6</v>
+      </c>
+      <c r="B9" s="13" t="inlineStr">
+        <is>
+          <t>API-025</t>
+        </is>
+      </c>
+      <c r="C9" s="13" t="inlineStr">
+        <is>
+          <t>POST</t>
+        </is>
+      </c>
+      <c r="D9" s="13" t="inlineStr">
+        <is>
+          <t>/api/attendance/break-end</t>
+        </is>
+      </c>
+      <c r="E9" s="13" t="inlineStr">
+        <is>
+          <t>全ロール（認証必須）</t>
+        </is>
+      </c>
+      <c r="F9" s="13" t="inlineStr">
+        <is>
+          <t>なし（本人・本日）</t>
+        </is>
+      </c>
+      <c r="G9" s="13" t="inlineStr">
+        <is>
+          <t>200 / {workDate, openKind, breaks[{kind, startAt, endAt}]}</t>
+        </is>
+      </c>
+      <c r="H9" s="13" t="inlineStr">
+        <is>
+          <t>E-007 / 409（出勤打刻なし）, E-006 / 409（退勤済み）, E-021 / 409（休憩中・離席中ではない）</t>
+        </is>
+      </c>
+      <c r="I9" s="13" t="inlineStr">
+        <is>
+          <t>AttendanceController#breakEnd</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="13" t="n">
+        <v>7</v>
+      </c>
+      <c r="B10" s="13" t="inlineStr">
+        <is>
+          <t>API-004</t>
+        </is>
+      </c>
+      <c r="C10" s="13" t="inlineStr">
+        <is>
+          <t>GET</t>
+        </is>
+      </c>
+      <c r="D10" s="13" t="inlineStr">
+        <is>
+          <t>/api/attendance</t>
+        </is>
+      </c>
+      <c r="E10" s="13" t="inlineStr">
+        <is>
+          <t>全ロール（認証必須）</t>
+        </is>
+      </c>
+      <c r="F10" s="13" t="inlineStr">
+        <is>
+          <t>クエリ: month=yyyy-MM（必須・未来月不可）</t>
+        </is>
+      </c>
+      <c r="G10" s="13" t="inlineStr">
+        <is>
+          <t>200 / {records[{workDate, clockIn, clockOut, workMinutes, overtimeMinutes, breaks[{kind, startAt, endAt}]}], totalWorkMinutes, totalOvertimeMinutes}</t>
+        </is>
+      </c>
+      <c r="H10" s="13" t="inlineStr">
+        <is>
+          <t>E-002 / 400</t>
+        </is>
+      </c>
+      <c r="I10" s="13" t="inlineStr">
+        <is>
+          <t>AttendanceController#getMonthly</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="13" t="n">
+        <v>8</v>
+      </c>
+      <c r="B11" s="13" t="inlineStr">
+        <is>
+          <t>API-005</t>
+        </is>
+      </c>
+      <c r="C11" s="13" t="inlineStr">
+        <is>
+          <t>POST</t>
+        </is>
+      </c>
+      <c r="D11" s="13" t="inlineStr">
+        <is>
+          <t>/api/requests</t>
+        </is>
+      </c>
+      <c r="E11" s="13" t="inlineStr">
+        <is>
+          <t>全ロール（認証必須）（申請者は常に本人）</t>
+        </is>
+      </c>
+      <c r="F11" s="13" t="inlineStr">
+        <is>
+          <t>本文: requestType（LEAVE|CLOCK_CORRECTION|BREAK_CORRECTION）, leaveTypeId, startDate, endDate, unit（FULL|AM|PM）, correctedClockIn/Out（HH:mm）, breakKind（BREAK|AWAY）, breakStart/breakEnd（HH:mm。休憩・離席修正。startDate が対象日）, reason（200 文字以内）, asDraft</t>
+        </is>
+      </c>
+      <c r="G11" s="13" t="inlineStr">
+        <is>
+          <t>201 / {requestId, status（DRAFT|PENDING）}</t>
+        </is>
+      </c>
+      <c r="H11" s="13" t="inlineStr">
+        <is>
+          <t>E-002, E-003 / 400（休憩・離席修正は出勤打刻なし・終了≦開始・出勤〜退勤の範囲外）, E-004 / 409, E-005 / 409（休憩・離席修正は他区間との重複・同日同種別の承認待ちを含む）, E-010 / 403</t>
+        </is>
+      </c>
+      <c r="I11" s="13" t="inlineStr">
+        <is>
+          <t>RequestController#create</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="13" t="n">
+        <v>9</v>
+      </c>
+      <c r="B12" s="13" t="inlineStr">
+        <is>
+          <t>API-006</t>
+        </is>
+      </c>
+      <c r="C12" s="13" t="inlineStr">
+        <is>
+          <t>GET</t>
+        </is>
+      </c>
+      <c r="D12" s="13" t="inlineStr">
+        <is>
+          <t>/api/requests</t>
+        </is>
+      </c>
+      <c r="E12" s="13" t="inlineStr">
+        <is>
+          <t>全ロール（認証必須）（本人の申請のみ）</t>
+        </is>
+      </c>
+      <c r="F12" s="13" t="inlineStr">
+        <is>
+          <t>クエリ: status（任意。6 値）</t>
+        </is>
+      </c>
+      <c r="G12" s="13" t="inlineStr">
+        <is>
+          <t>200 / {requests[{requestId, requestType, leaveTypeName, startDate, endDate, unit, days, status, submittedAt, createdAt}]}</t>
+        </is>
+      </c>
+      <c r="H12" s="13" t="inlineStr">
+        <is>
+          <t>E-002 / 400</t>
+        </is>
+      </c>
+      <c r="I12" s="13" t="inlineStr">
+        <is>
+          <t>RequestController#list</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="13" t="n">
+        <v>10</v>
+      </c>
+      <c r="B13" s="13" t="inlineStr">
+        <is>
+          <t>API-007</t>
+        </is>
+      </c>
+      <c r="C13" s="13" t="inlineStr">
+        <is>
+          <t>GET</t>
+        </is>
+      </c>
+      <c r="D13" s="13" t="inlineStr">
+        <is>
+          <t>/api/requests/{id}</t>
+        </is>
+      </c>
+      <c r="E13" s="13" t="inlineStr">
+        <is>
+          <t>全ロール（認証必須）（本人・承認者・ADMIN。他人の下書きは不可）</t>
+        </is>
+      </c>
+      <c r="F13" s="13" t="inlineStr">
+        <is>
+          <t>パス: id</t>
+        </is>
+      </c>
+      <c r="G13" s="13" t="inlineStr">
+        <is>
+          <t>200 / {request{requestId, requestType, applicantId, applicantName, departmentName, leaveTypeId, leaveTypeName, startDate, endDate, unit, days, correctedClockIn, correctedClockOut, breakKind, breakStart, breakEnd, reason, status, currentStep, submittedAt, createdAt}, steps[{stepNo, stepName, approverId, approverName, status, comment, actedAt, current}]（steps[].status は WAITING|APPROVED|RETURNED|REJECTED|SKIPPED。SKIPPED は取下げ・差戻し・却下で打ち切られた未処理の段の表示専用値）, applicantBalance}</t>
+        </is>
+      </c>
+      <c r="H13" s="13" t="inlineStr">
+        <is>
+          <t>E-002 / 400, E-010 / 403（不存在・閲覧権限なしを区別しない）</t>
+        </is>
+      </c>
+      <c r="I13" s="13" t="inlineStr">
+        <is>
+          <t>RequestController#detail</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="13" t="n">
+        <v>11</v>
+      </c>
+      <c r="B14" s="13" t="inlineStr">
+        <is>
+          <t>API-008</t>
+        </is>
+      </c>
+      <c r="C14" s="13" t="inlineStr">
+        <is>
+          <t>POST</t>
+        </is>
+      </c>
+      <c r="D14" s="13" t="inlineStr">
+        <is>
+          <t>/api/requests/{id}/withdraw</t>
+        </is>
+      </c>
+      <c r="E14" s="13" t="inlineStr">
+        <is>
+          <t>全ロール（認証必須）（本人のみ）</t>
+        </is>
+      </c>
+      <c r="F14" s="13" t="inlineStr">
+        <is>
+          <t>パス: id</t>
+        </is>
+      </c>
+      <c r="G14" s="13" t="inlineStr">
+        <is>
+          <t>200 / {status: "WITHDRAWN"}</t>
+        </is>
+      </c>
+      <c r="H14" s="13" t="inlineStr">
+        <is>
+          <t>E-010 / 403, E-011 / 409（承認済み・却下・取下げ済み）</t>
+        </is>
+      </c>
+      <c r="I14" s="13" t="inlineStr">
+        <is>
+          <t>RequestController#withdraw</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="13" t="n">
+        <v>12</v>
+      </c>
+      <c r="B15" s="13" t="inlineStr">
+        <is>
+          <t>API-022</t>
+        </is>
+      </c>
+      <c r="C15" s="13" t="inlineStr">
+        <is>
+          <t>POST</t>
+        </is>
+      </c>
+      <c r="D15" s="13" t="inlineStr">
+        <is>
+          <t>/api/requests/{id}/submit</t>
+        </is>
+      </c>
+      <c r="E15" s="13" t="inlineStr">
+        <is>
+          <t>全ロール（認証必須）（本人のみ）</t>
+        </is>
+      </c>
+      <c r="F15" s="13" t="inlineStr">
+        <is>
+          <t>パス: id</t>
+        </is>
+      </c>
+      <c r="G15" s="13" t="inlineStr">
+        <is>
+          <t>200 / {requestId, status: "PENDING"}</t>
+        </is>
+      </c>
+      <c r="H15" s="13" t="inlineStr">
+        <is>
+          <t>E-015 / 404, E-010 / 403, E-016 / 409（下書き・差戻し以外）, E-002, E-003, E-004, E-005</t>
+        </is>
+      </c>
+      <c r="I15" s="13" t="inlineStr">
+        <is>
+          <t>RequestController#submit</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="13" t="n">
+        <v>13</v>
+      </c>
+      <c r="B16" s="13" t="inlineStr">
+        <is>
+          <t>API-009</t>
+        </is>
+      </c>
+      <c r="C16" s="13" t="inlineStr">
+        <is>
+          <t>GET</t>
+        </is>
+      </c>
+      <c r="D16" s="13" t="inlineStr">
+        <is>
+          <t>/api/approvals/pending</t>
+        </is>
+      </c>
+      <c r="E16" s="13" t="inlineStr">
+        <is>
+          <t>@PreAuthorize MANAGER|ADMIN（＋DB で ACTIVE と再確認）</t>
+        </is>
+      </c>
+      <c r="F16" s="13" t="inlineStr">
+        <is>
+          <t>クエリ: requestType（LEAVE|CLOCK_CORRECTION|BREAK_CORRECTION）, stepNo（1|2）</t>
+        </is>
+      </c>
+      <c r="G16" s="13" t="inlineStr">
+        <is>
+          <t>200 / {items[{stepId, stepNo, requestId, requestType, applicantId, applicantName, departmentName, startDate, endDate, days, submittedAt, step1ApprovedAt}]}</t>
+        </is>
+      </c>
+      <c r="H16" s="13" t="inlineStr">
+        <is>
+          <t>E-002 / 400, E-010 / 403</t>
+        </is>
+      </c>
+      <c r="I16" s="13" t="inlineStr">
+        <is>
+          <t>ApprovalController#pending</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="13" t="n">
+        <v>14</v>
+      </c>
+      <c r="B17" s="13" t="inlineStr">
+        <is>
+          <t>API-010</t>
+        </is>
+      </c>
+      <c r="C17" s="13" t="inlineStr">
+        <is>
+          <t>POST</t>
+        </is>
+      </c>
+      <c r="D17" s="13" t="inlineStr">
+        <is>
+          <t>/api/approvals/{stepId}/approve</t>
+        </is>
+      </c>
+      <c r="E17" s="13" t="inlineStr">
+        <is>
+          <t>@PreAuthorize MANAGER|ADMIN。1 段目は指名された本人、2 段目は ADMIN</t>
+        </is>
+      </c>
+      <c r="F17" s="13" t="inlineStr">
+        <is>
+          <t>パス: stepId（承認ステップ ID）。本文（省略可）: comment（500 文字以内）</t>
+        </is>
+      </c>
+      <c r="G17" s="13" t="inlineStr">
+        <is>
+          <t>200 / {requestStatus（PENDING|APPROVED）}</t>
+        </is>
+      </c>
+      <c r="H17" s="13" t="inlineStr">
+        <is>
+          <t>E-010 / 403, E-009 / 403（自分の申請）, E-011 / 409</t>
+        </is>
+      </c>
+      <c r="I17" s="13" t="inlineStr">
+        <is>
+          <t>ApprovalController#approve</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="13" t="n">
+        <v>15</v>
+      </c>
+      <c r="B18" s="13" t="inlineStr">
+        <is>
+          <t>API-011</t>
+        </is>
+      </c>
+      <c r="C18" s="13" t="inlineStr">
+        <is>
+          <t>POST</t>
+        </is>
+      </c>
+      <c r="D18" s="13" t="inlineStr">
+        <is>
+          <t>/api/approvals/{stepId}/return</t>
+        </is>
+      </c>
+      <c r="E18" s="13" t="inlineStr">
+        <is>
+          <t>同上</t>
+        </is>
+      </c>
+      <c r="F18" s="13" t="inlineStr">
+        <is>
+          <t>パス: stepId。本文: comment（必須。500 文字以内）</t>
+        </is>
+      </c>
+      <c r="G18" s="13" t="inlineStr">
+        <is>
+          <t>200 / {requestStatus: "RETURNED"}</t>
+        </is>
+      </c>
+      <c r="H18" s="13" t="inlineStr">
+        <is>
+          <t>E-008 / 400, E-010 / 403, E-009 / 403, E-011 / 409</t>
+        </is>
+      </c>
+      <c r="I18" s="13" t="inlineStr">
+        <is>
+          <t>ApprovalController#returnBack</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="13" t="n">
+        <v>16</v>
+      </c>
+      <c r="B19" s="13" t="inlineStr">
+        <is>
+          <t>API-012</t>
+        </is>
+      </c>
+      <c r="C19" s="13" t="inlineStr">
+        <is>
+          <t>POST</t>
+        </is>
+      </c>
+      <c r="D19" s="13" t="inlineStr">
+        <is>
+          <t>/api/approvals/{stepId}/reject</t>
+        </is>
+      </c>
+      <c r="E19" s="13" t="inlineStr">
+        <is>
+          <t>同上</t>
+        </is>
+      </c>
+      <c r="F19" s="13" t="inlineStr">
+        <is>
+          <t>パス: stepId。本文: comment（必須。500 文字以内）</t>
+        </is>
+      </c>
+      <c r="G19" s="13" t="inlineStr">
+        <is>
+          <t>200 / {requestStatus: "REJECTED"}</t>
+        </is>
+      </c>
+      <c r="H19" s="13" t="inlineStr">
+        <is>
+          <t>E-008 / 400, E-010 / 403, E-009 / 403, E-011 / 409</t>
+        </is>
+      </c>
+      <c r="I19" s="13" t="inlineStr">
+        <is>
+          <t>ApprovalController#reject</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="13" t="n">
+        <v>17</v>
+      </c>
+      <c r="B20" s="13" t="inlineStr">
+        <is>
+          <t>API-013</t>
+        </is>
+      </c>
+      <c r="C20" s="13" t="inlineStr">
+        <is>
+          <t>GET</t>
+        </is>
+      </c>
+      <c r="D20" s="13" t="inlineStr">
+        <is>
+          <t>/api/leave-balances</t>
+        </is>
+      </c>
+      <c r="E20" s="13" t="inlineStr">
+        <is>
+          <t>全ロール（認証必須）（本人のみ）</t>
+        </is>
+      </c>
+      <c r="F20" s="13" t="inlineStr">
+        <is>
+          <t>なし</t>
+        </is>
+      </c>
+      <c r="G20" s="13" t="inlineStr">
+        <is>
+          <t>200 / {asOf, balances[{leaveTypeId, leaveTypeName, annual, grantedDays, usedDays, remainingDays, expiresOn, grants[{balanceId, grantedOn, expiresOn, grantedDays, usedDays, remainingDays}]}], mandatory5{target, requiredDays, takenDays, shortageDays, achieved, periodStart, periodEnd, grantedDays}, nextGrantDate}</t>
+        </is>
+      </c>
+      <c r="H20" s="13" t="inlineStr">
+        <is>
+          <t>E-015 / 404</t>
+        </is>
+      </c>
+      <c r="I20" s="13" t="inlineStr">
+        <is>
+          <t>LeaveBalanceController#getBalances</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="13" t="n">
+        <v>18</v>
+      </c>
+      <c r="B21" s="13" t="inlineStr">
+        <is>
+          <t>API-021</t>
+        </is>
+      </c>
+      <c r="C21" s="13" t="inlineStr">
+        <is>
+          <t>GET</t>
+        </is>
+      </c>
+      <c r="D21" s="13" t="inlineStr">
+        <is>
+          <t>/api/leave-types</t>
+        </is>
+      </c>
+      <c r="E21" s="13" t="inlineStr">
+        <is>
+          <t>全ロール（認証必須）</t>
+        </is>
+      </c>
+      <c r="F21" s="13" t="inlineStr">
+        <is>
+          <t>なし</t>
+        </is>
+      </c>
+      <c r="G21" s="13" t="inlineStr">
+        <is>
+          <t>200 / {leaveTypes[{id, name, isPaid, maxDaysRule, allowHalfDay}]}（有効のみ）</t>
+        </is>
+      </c>
+      <c r="H21" s="13" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I21" s="13" t="inlineStr">
+        <is>
+          <t>LeaveTypeController#list</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="13" t="n">
+        <v>19</v>
+      </c>
+      <c r="B22" s="13" t="inlineStr">
+        <is>
+          <t>API-026</t>
+        </is>
+      </c>
+      <c r="C22" s="13" t="inlineStr">
+        <is>
+          <t>GET</t>
+        </is>
+      </c>
+      <c r="D22" s="13" t="inlineStr">
+        <is>
+          <t>/api/departments</t>
+        </is>
+      </c>
+      <c r="E22" s="13" t="inlineStr">
+        <is>
+          <t>全ロール（認証必須）</t>
+        </is>
+      </c>
+      <c r="F22" s="13" t="inlineStr">
+        <is>
+          <t>なし</t>
+        </is>
+      </c>
+      <c r="G22" s="13" t="inlineStr">
+        <is>
+          <t>200 / {departments[{id, name}]}（id 昇順）</t>
+        </is>
+      </c>
+      <c r="H22" s="13" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I22" s="13" t="inlineStr">
+        <is>
+          <t>DepartmentController#list</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="13" t="n">
+        <v>20</v>
+      </c>
+      <c r="B23" s="13" t="inlineStr">
+        <is>
+          <t>API-014</t>
+        </is>
+      </c>
+      <c r="C23" s="13" t="inlineStr">
+        <is>
+          <t>GET</t>
+        </is>
+      </c>
+      <c r="D23" s="13" t="inlineStr">
+        <is>
+          <t>/api/admin/users</t>
+        </is>
+      </c>
+      <c r="E23" s="13" t="inlineStr">
+        <is>
+          <t>ADMIN（SecurityConfig /api/admin/** ＋ @PreAuthorize）</t>
+        </is>
+      </c>
+      <c r="F23" s="13" t="inlineStr">
+        <is>
+          <t>クエリ: keyword（100 文字以内）, role, status, departmentId</t>
+        </is>
+      </c>
+      <c r="G23" s="13" t="inlineStr">
+        <is>
+          <t>200 / {users[{id, name, email, role, departmentId, departmentName, managerId, managerName, hireDate, status}], total}</t>
+        </is>
+      </c>
+      <c r="H23" s="13" t="inlineStr">
+        <is>
+          <t>E-002 / 400</t>
+        </is>
+      </c>
+      <c r="I23" s="13" t="inlineStr">
+        <is>
+          <t>AdminUserController#list</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="13" t="n">
+        <v>21</v>
+      </c>
+      <c r="B24" s="13" t="inlineStr">
+        <is>
+          <t>API-014</t>
+        </is>
+      </c>
+      <c r="C24" s="13" t="inlineStr">
+        <is>
+          <t>GET</t>
+        </is>
+      </c>
+      <c r="D24" s="13" t="inlineStr">
+        <is>
+          <t>/api/admin/users/{id}</t>
+        </is>
+      </c>
+      <c r="E24" s="13" t="inlineStr">
+        <is>
+          <t>ADMIN</t>
+        </is>
+      </c>
+      <c r="F24" s="13" t="inlineStr">
+        <is>
+          <t>パス: id</t>
+        </is>
+      </c>
+      <c r="G24" s="13" t="inlineStr">
+        <is>
+          <t>200 / {user}</t>
+        </is>
+      </c>
+      <c r="H24" s="13" t="inlineStr">
+        <is>
+          <t>E-015 / 404</t>
+        </is>
+      </c>
+      <c r="I24" s="13" t="inlineStr">
+        <is>
+          <t>AdminUserController#get</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="13" t="n">
+        <v>22</v>
+      </c>
+      <c r="B25" s="13" t="inlineStr">
+        <is>
+          <t>API-014</t>
+        </is>
+      </c>
+      <c r="C25" s="13" t="inlineStr">
+        <is>
+          <t>POST</t>
+        </is>
+      </c>
+      <c r="D25" s="13" t="inlineStr">
+        <is>
+          <t>/api/admin/users</t>
+        </is>
+      </c>
+      <c r="E25" s="13" t="inlineStr">
+        <is>
+          <t>ADMIN</t>
+        </is>
+      </c>
+      <c r="F25" s="13" t="inlineStr">
+        <is>
+          <t>本文: name, email, initialPassword（12〜72 文字・半角英数字記号・英字と数字を両方含む）, role, departmentId, managerId, hireDate</t>
+        </is>
+      </c>
+      <c r="G25" s="13" t="inlineStr">
+        <is>
+          <t>201 / {user}（must_change_password=true で登録）</t>
+        </is>
+      </c>
+      <c r="H25" s="13" t="inlineStr">
+        <is>
+          <t>E-002 / 400（パスワードポリシー違反を含む）, E-013 / 409（メール重複）, E-014 / 400（所属・上長）</t>
+        </is>
+      </c>
+      <c r="I25" s="13" t="inlineStr">
+        <is>
+          <t>AdminUserController#create</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="13" t="n">
+        <v>23</v>
+      </c>
+      <c r="B26" s="13" t="inlineStr">
+        <is>
+          <t>API-014</t>
+        </is>
+      </c>
+      <c r="C26" s="13" t="inlineStr">
+        <is>
+          <t>PUT</t>
+        </is>
+      </c>
+      <c r="D26" s="13" t="inlineStr">
+        <is>
+          <t>/api/admin/users/{id}</t>
+        </is>
+      </c>
+      <c r="E26" s="13" t="inlineStr">
+        <is>
+          <t>ADMIN</t>
+        </is>
+      </c>
+      <c r="F26" s="13" t="inlineStr">
+        <is>
+          <t>本文: name, email, role, departmentId, managerId, hireDate, status（ACTIVE|INACTIVE）。全項目置換</t>
+        </is>
+      </c>
+      <c r="G26" s="13" t="inlineStr">
+        <is>
+          <t>200 / {user}</t>
+        </is>
+      </c>
+      <c r="H26" s="13" t="inlineStr">
+        <is>
+          <t>E-002, E-010 / 403（自分自身の無効化・ロール降格）, E-013, E-014, E-015, E-016 / 409（有効な部下がいる上長の無効化・従業員化）</t>
+        </is>
+      </c>
+      <c r="I26" s="13" t="inlineStr">
+        <is>
+          <t>AdminUserController#update</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="13" t="n">
+        <v>24</v>
+      </c>
+      <c r="B27" s="13" t="inlineStr">
+        <is>
+          <t>API-014</t>
+        </is>
+      </c>
+      <c r="C27" s="13" t="inlineStr">
+        <is>
+          <t>PUT</t>
+        </is>
+      </c>
+      <c r="D27" s="13" t="inlineStr">
+        <is>
+          <t>/api/admin/users/{id}/password</t>
+        </is>
+      </c>
+      <c r="E27" s="13" t="inlineStr">
+        <is>
+          <t>ADMIN</t>
+        </is>
+      </c>
+      <c r="F27" s="13" t="inlineStr">
+        <is>
+          <t>本文: newPassword（12〜72 文字・半角英数字記号・英字と数字を両方含む）</t>
+        </is>
+      </c>
+      <c r="G27" s="13" t="inlineStr">
+        <is>
+          <t>200 / {user}（must_change_password=true、失敗回数・ロックを解除。以前に発行されたトークンは失効）</t>
+        </is>
+      </c>
+      <c r="H27" s="13" t="inlineStr">
+        <is>
+          <t>E-002 / 400（パスワードポリシー違反を含む）, E-015 / 404</t>
+        </is>
+      </c>
+      <c r="I27" s="13" t="inlineStr">
+        <is>
+          <t>AdminUserController#resetPassword</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="13" t="n">
+        <v>25</v>
+      </c>
+      <c r="B28" s="13" t="inlineStr">
+        <is>
+          <t>API-015</t>
+        </is>
+      </c>
+      <c r="C28" s="13" t="inlineStr">
+        <is>
+          <t>GET</t>
+        </is>
+      </c>
+      <c r="D28" s="13" t="inlineStr">
+        <is>
+          <t>/api/admin/leave-types</t>
+        </is>
+      </c>
+      <c r="E28" s="13" t="inlineStr">
+        <is>
+          <t>ADMIN</t>
+        </is>
+      </c>
+      <c r="F28" s="13" t="inlineStr">
+        <is>
+          <t>クエリ: activeOnly（既定 false）</t>
+        </is>
+      </c>
+      <c r="G28" s="13" t="inlineStr">
+        <is>
+          <t>200 / {leaveTypes[{id, name, legalBasis, isPaid, maxDaysRule, allowHalfDay, isActive}]}</t>
+        </is>
+      </c>
+      <c r="H28" s="13" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I28" s="13" t="inlineStr">
+        <is>
+          <t>AdminLeaveTypeController#list</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="13" t="n">
+        <v>26</v>
+      </c>
+      <c r="B29" s="13" t="inlineStr">
+        <is>
+          <t>API-015</t>
+        </is>
+      </c>
+      <c r="C29" s="13" t="inlineStr">
+        <is>
+          <t>GET</t>
+        </is>
+      </c>
+      <c r="D29" s="13" t="inlineStr">
+        <is>
+          <t>/api/admin/leave-types/{id}</t>
+        </is>
+      </c>
+      <c r="E29" s="13" t="inlineStr">
+        <is>
+          <t>ADMIN</t>
+        </is>
+      </c>
+      <c r="F29" s="13" t="inlineStr">
+        <is>
+          <t>パス: id</t>
+        </is>
+      </c>
+      <c r="G29" s="13" t="inlineStr">
+        <is>
+          <t>200 / {leaveType}</t>
+        </is>
+      </c>
+      <c r="H29" s="13" t="inlineStr">
+        <is>
+          <t>E-015 / 404</t>
+        </is>
+      </c>
+      <c r="I29" s="13" t="inlineStr">
+        <is>
+          <t>AdminLeaveTypeController#get</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="13" t="n">
+        <v>27</v>
+      </c>
+      <c r="B30" s="13" t="inlineStr">
+        <is>
+          <t>API-015</t>
+        </is>
+      </c>
+      <c r="C30" s="13" t="inlineStr">
+        <is>
+          <t>POST</t>
+        </is>
+      </c>
+      <c r="D30" s="13" t="inlineStr">
+        <is>
+          <t>/api/admin/leave-types</t>
+        </is>
+      </c>
+      <c r="E30" s="13" t="inlineStr">
+        <is>
+          <t>ADMIN</t>
+        </is>
+      </c>
+      <c r="F30" s="13" t="inlineStr">
+        <is>
+          <t>本文: name, legalBasis, isPaid, maxDaysRule（LIMITED|UNLIMITED）, allowHalfDay, isActive</t>
+        </is>
+      </c>
+      <c r="G30" s="13" t="inlineStr">
+        <is>
+          <t>201 / {leaveType}</t>
+        </is>
+      </c>
+      <c r="H30" s="13" t="inlineStr">
+        <is>
+          <t>E-002 / 400, E-013 / 409（名称重複）</t>
+        </is>
+      </c>
+      <c r="I30" s="13" t="inlineStr">
+        <is>
+          <t>AdminLeaveTypeController#create</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="13" t="n">
+        <v>28</v>
+      </c>
+      <c r="B31" s="13" t="inlineStr">
+        <is>
+          <t>API-015</t>
+        </is>
+      </c>
+      <c r="C31" s="13" t="inlineStr">
+        <is>
+          <t>PUT</t>
+        </is>
+      </c>
+      <c r="D31" s="13" t="inlineStr">
+        <is>
+          <t>/api/admin/leave-types/{id}</t>
+        </is>
+      </c>
+      <c r="E31" s="13" t="inlineStr">
+        <is>
+          <t>ADMIN</t>
+        </is>
+      </c>
+      <c r="F31" s="13" t="inlineStr">
+        <is>
+          <t>本文: POST と同じ（全項目置換）</t>
+        </is>
+      </c>
+      <c r="G31" s="13" t="inlineStr">
+        <is>
+          <t>200 / {leaveType}</t>
+        </is>
+      </c>
+      <c r="H31" s="13" t="inlineStr">
+        <is>
+          <t>E-002, E-013, E-015, E-016 / 409（年次有給休暇の固定項目の変更）</t>
+        </is>
+      </c>
+      <c r="I31" s="13" t="inlineStr">
+        <is>
+          <t>AdminLeaveTypeController#update</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="13" t="n">
+        <v>29</v>
+      </c>
+      <c r="B32" s="13" t="inlineStr">
+        <is>
+          <t>API-016</t>
+        </is>
+      </c>
+      <c r="C32" s="13" t="inlineStr">
+        <is>
+          <t>GET</t>
+        </is>
+      </c>
+      <c r="D32" s="13" t="inlineStr">
+        <is>
+          <t>/api/admin/holidays</t>
+        </is>
+      </c>
+      <c r="E32" s="13" t="inlineStr">
+        <is>
+          <t>ADMIN</t>
+        </is>
+      </c>
+      <c r="F32" s="13" t="inlineStr">
+        <is>
+          <t>クエリ: year（2000〜2099。省略時は本年）</t>
+        </is>
+      </c>
+      <c r="G32" s="13" t="inlineStr">
+        <is>
+          <t>200 / {year, holidays[{id, holidayDate, name}]}</t>
+        </is>
+      </c>
+      <c r="H32" s="13" t="inlineStr">
+        <is>
+          <t>E-002 / 400</t>
+        </is>
+      </c>
+      <c r="I32" s="13" t="inlineStr">
+        <is>
+          <t>AdminHolidayController#list</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="13" t="n">
+        <v>30</v>
+      </c>
+      <c r="B33" s="13" t="inlineStr">
+        <is>
+          <t>API-016</t>
+        </is>
+      </c>
+      <c r="C33" s="13" t="inlineStr">
+        <is>
+          <t>POST</t>
+        </is>
+      </c>
+      <c r="D33" s="13" t="inlineStr">
+        <is>
+          <t>/api/admin/holidays</t>
+        </is>
+      </c>
+      <c r="E33" s="13" t="inlineStr">
+        <is>
+          <t>ADMIN</t>
+        </is>
+      </c>
+      <c r="F33" s="13" t="inlineStr">
+        <is>
+          <t>本文: holidayDate, name（100 文字以内）</t>
+        </is>
+      </c>
+      <c r="G33" s="13" t="inlineStr">
+        <is>
+          <t>201 / {holiday}</t>
+        </is>
+      </c>
+      <c r="H33" s="13" t="inlineStr">
+        <is>
+          <t>E-002 / 400（2000〜2099 年外を含む）, E-013 / 409（日付重複）</t>
+        </is>
+      </c>
+      <c r="I33" s="13" t="inlineStr">
+        <is>
+          <t>AdminHolidayController#create</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="13" t="n">
+        <v>31</v>
+      </c>
+      <c r="B34" s="13" t="inlineStr">
+        <is>
+          <t>API-016</t>
+        </is>
+      </c>
+      <c r="C34" s="13" t="inlineStr">
+        <is>
+          <t>DELETE</t>
+        </is>
+      </c>
+      <c r="D34" s="13" t="inlineStr">
+        <is>
+          <t>/api/admin/holidays/{id}</t>
+        </is>
+      </c>
+      <c r="E34" s="13" t="inlineStr">
+        <is>
+          <t>ADMIN</t>
+        </is>
+      </c>
+      <c r="F34" s="13" t="inlineStr">
+        <is>
+          <t>パス: id</t>
+        </is>
+      </c>
+      <c r="G34" s="13" t="inlineStr">
+        <is>
+          <t>200 / {holiday}（削除した行）</t>
+        </is>
+      </c>
+      <c r="H34" s="13" t="inlineStr">
+        <is>
+          <t>E-015 / 404</t>
+        </is>
+      </c>
+      <c r="I34" s="13" t="inlineStr">
+        <is>
+          <t>AdminHolidayController#delete</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="13" t="n">
+        <v>32</v>
+      </c>
+      <c r="B35" s="13" t="inlineStr">
+        <is>
+          <t>API-017</t>
+        </is>
+      </c>
+      <c r="C35" s="13" t="inlineStr">
+        <is>
+          <t>GET</t>
+        </is>
+      </c>
+      <c r="D35" s="13" t="inlineStr">
+        <is>
+          <t>/api/admin/leave-grants</t>
+        </is>
+      </c>
+      <c r="E35" s="13" t="inlineStr">
+        <is>
+          <t>ADMIN</t>
+        </is>
+      </c>
+      <c r="F35" s="13" t="inlineStr">
+        <is>
+          <t>クエリ: userId（必須）, leaveTypeId（任意）</t>
+        </is>
+      </c>
+      <c r="G35" s="13" t="inlineStr">
+        <is>
+          <t>200 / {userId, userName, hireDate, nextGrantDate, nextStatutoryDays, grants[{id, leaveTypeId, leaveTypeName, grantedOn, grantedDays, usedDays, remainingDays, expiresOn, expired}]}</t>
+        </is>
+      </c>
+      <c r="H35" s="13" t="inlineStr">
+        <is>
+          <t>E-002 / 400, E-015 / 404</t>
+        </is>
+      </c>
+      <c r="I35" s="13" t="inlineStr">
+        <is>
+          <t>AdminLeaveGrantController#list</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="13" t="n">
+        <v>33</v>
+      </c>
+      <c r="B36" s="13" t="inlineStr">
+        <is>
+          <t>API-017</t>
+        </is>
+      </c>
+      <c r="C36" s="13" t="inlineStr">
+        <is>
+          <t>POST</t>
+        </is>
+      </c>
+      <c r="D36" s="13" t="inlineStr">
+        <is>
+          <t>/api/admin/leave-grants</t>
+        </is>
+      </c>
+      <c r="E36" s="13" t="inlineStr">
+        <is>
+          <t>ADMIN</t>
+        </is>
+      </c>
+      <c r="F36" s="13" t="inlineStr">
+        <is>
+          <t>本文: userId, leaveTypeId, grantedOn, grantedDays（0.1〜99.9・小数 1 位）, note（200 文字以内）</t>
+        </is>
+      </c>
+      <c r="G36" s="13" t="inlineStr">
+        <is>
+          <t>201 / {grant}（付与行 1 件。本人へ LEAVE_GRANTED 通知）</t>
+        </is>
+      </c>
+      <c r="H36" s="13" t="inlineStr">
+        <is>
+          <t>E-002, E-003 / 400, E-013 / 409, E-014 / 400（無効ユーザー・UNLIMITED／無効な種別・付与日不正）, E-015 / 404</t>
+        </is>
+      </c>
+      <c r="I36" s="13" t="inlineStr">
+        <is>
+          <t>AdminLeaveGrantController#create</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="13" t="n">
+        <v>34</v>
+      </c>
+      <c r="B37" s="13" t="inlineStr">
+        <is>
+          <t>API-017</t>
+        </is>
+      </c>
+      <c r="C37" s="13" t="inlineStr">
+        <is>
+          <t>PUT</t>
+        </is>
+      </c>
+      <c r="D37" s="13" t="inlineStr">
+        <is>
+          <t>/api/admin/leave-grants/{id}</t>
+        </is>
+      </c>
+      <c r="E37" s="13" t="inlineStr">
+        <is>
+          <t>ADMIN</t>
+        </is>
+      </c>
+      <c r="F37" s="13" t="inlineStr">
+        <is>
+          <t>本文: grantedDays, note（200 文字以内）。付与日数の上書き</t>
+        </is>
+      </c>
+      <c r="G37" s="13" t="inlineStr">
+        <is>
+          <t>200 / {grant}（変更時のみ本人へ通知）</t>
+        </is>
+      </c>
+      <c r="H37" s="13" t="inlineStr">
+        <is>
+          <t>E-002, E-003 / 400, E-004 / 409（消化済み日数を下回る）, E-015 / 404</t>
+        </is>
+      </c>
+      <c r="I37" s="13" t="inlineStr">
+        <is>
+          <t>AdminLeaveGrantController#adjust</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="13" t="n">
+        <v>35</v>
+      </c>
+      <c r="B38" s="13" t="inlineStr">
+        <is>
+          <t>API-018</t>
+        </is>
+      </c>
+      <c r="C38" s="13" t="inlineStr">
+        <is>
+          <t>GET</t>
+        </is>
+      </c>
+      <c r="D38" s="13" t="inlineStr">
+        <is>
+          <t>/api/admin/reports/monthly</t>
+        </is>
+      </c>
+      <c r="E38" s="13" t="inlineStr">
+        <is>
+          <t>ADMIN</t>
+        </is>
+      </c>
+      <c r="F38" s="13" t="inlineStr">
+        <is>
+          <t>クエリ: month=yyyy-MM（必須）, departmentId（任意）, format=json|csv（既定 json）</t>
+        </is>
+      </c>
+      <c r="G38" s="13" t="inlineStr">
+        <is>
+          <t>200 / format=json: {month, departmentId, rows[{userId, userName, departmentName, workDays, workMinutes, overtimeMinutes, leaveDays}]}。format=csv: text/csv（UTF-8 BOM・CRLF）、Content-Disposition: attachment; filename=kintai_summary_yyyyMM.csv、Cache-Control: no-store</t>
+        </is>
+      </c>
+      <c r="H38" s="13" t="inlineStr">
+        <is>
+          <t>E-002 / 400（month 未指定・形式不正・format 不正）</t>
+        </is>
+      </c>
+      <c r="I38" s="13" t="inlineStr">
+        <is>
+          <t>AdminReportController#monthly</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="13" t="n">
+        <v>36</v>
+      </c>
+      <c r="B39" s="13" t="inlineStr">
+        <is>
+          <t>API-019</t>
+        </is>
+      </c>
+      <c r="C39" s="13" t="inlineStr">
+        <is>
+          <t>GET</t>
+        </is>
+      </c>
+      <c r="D39" s="13" t="inlineStr">
+        <is>
+          <t>/api/notifications</t>
+        </is>
+      </c>
+      <c r="E39" s="13" t="inlineStr">
+        <is>
+          <t>全ロール（認証必須）（本人のみ）</t>
+        </is>
+      </c>
+      <c r="F39" s="13" t="inlineStr">
+        <is>
+          <t>なし</t>
+        </is>
+      </c>
+      <c r="G39" s="13" t="inlineStr">
+        <is>
+          <t>200 / {notifications[{id, type, message, requestId, createdAt, isRead}]}（新しい順・最大 50 件）</t>
+        </is>
+      </c>
+      <c r="H39" s="13" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I39" s="13" t="inlineStr">
+        <is>
+          <t>NotificationController#list</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="13" t="n">
+        <v>37</v>
+      </c>
+      <c r="B40" s="13" t="inlineStr">
+        <is>
+          <t>API-019</t>
+        </is>
+      </c>
+      <c r="C40" s="13" t="inlineStr">
+        <is>
+          <t>POST</t>
+        </is>
+      </c>
+      <c r="D40" s="13" t="inlineStr">
+        <is>
+          <t>/api/notifications/{id}/read</t>
+        </is>
+      </c>
+      <c r="E40" s="13" t="inlineStr">
+        <is>
+          <t>全ロール（認証必須）（本人のみ）</t>
+        </is>
+      </c>
+      <c r="F40" s="13" t="inlineStr">
+        <is>
+          <t>パス: id</t>
+        </is>
+      </c>
+      <c r="G40" s="13" t="inlineStr">
+        <is>
+          <t>200 / 通知 1 件 {id, type, message, requestId, createdAt, isRead}（冪等）</t>
+        </is>
+      </c>
+      <c r="H40" s="13" t="inlineStr">
+        <is>
+          <t>E-010 / 403（不存在・他人の通知を区別しない）</t>
+        </is>
+      </c>
+      <c r="I40" s="13" t="inlineStr">
+        <is>
+          <t>NotificationController#markAsRead</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="13" t="n">
+        <v>38</v>
+      </c>
+      <c r="B41" s="13" t="inlineStr">
+        <is>
+          <t>API-020</t>
+        </is>
+      </c>
+      <c r="C41" s="13" t="inlineStr">
+        <is>
+          <t>GET</t>
+        </is>
+      </c>
+      <c r="D41" s="13" t="inlineStr">
+        <is>
+          <t>/api/manager/subordinates/summary</t>
+        </is>
+      </c>
+      <c r="E41" s="13" t="inlineStr">
+        <is>
+          <t>@PreAuthorize MANAGER のみ</t>
+        </is>
+      </c>
+      <c r="F41" s="13" t="inlineStr">
+        <is>
+          <t>クエリ: month=yyyy-MM（必須）</t>
+        </is>
+      </c>
+      <c r="G41" s="13" t="inlineStr">
+        <is>
+          <t>200 / {month, rows[{userId, userName, departmentName, workDays, workMinutes, overtimeMinutes, leaveDays}]}（users.manager_id が自分の部下）</t>
+        </is>
+      </c>
+      <c r="H41" s="13" t="inlineStr">
+        <is>
+          <t>E-002 / 400, E-010 / 403（管理者を含む）</t>
+        </is>
+      </c>
+      <c r="I41" s="13" t="inlineStr">
+        <is>
+          <t>ManagerController#subordinatesSummary</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="13" t="n">
+        <v>39</v>
+      </c>
+      <c r="B42" s="13" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C42" s="13" t="inlineStr">
+        <is>
+          <t>GET</t>
+        </is>
+      </c>
+      <c r="D42" s="13" t="inlineStr">
+        <is>
+          <t>/actuator/health</t>
+        </is>
+      </c>
+      <c r="E42" s="13" t="inlineStr">
+        <is>
+          <t>permitAll（/actuator/health/** を含む）</t>
+        </is>
+      </c>
+      <c r="F42" s="13" t="inlineStr">
+        <is>
+          <t>なし</t>
+        </is>
+      </c>
+      <c r="G42" s="13" t="inlineStr">
+        <is>
+          <t>200 / Actuator health（probes 有効）</t>
+        </is>
+      </c>
+      <c r="H42" s="13" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I42" s="13" t="inlineStr">
+        <is>
+          <t>Spring Boot Actuator</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="landscape"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:B10"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="24" customWidth="1" min="1" max="1"/>
+    <col width="130" customWidth="1" min="2" max="2"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="12" t="inlineStr">
+        <is>
+          <t>項目</t>
+        </is>
+      </c>
+      <c r="B1" s="12" t="inlineStr">
+        <is>
+          <t>内容</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="13" t="inlineStr">
+        <is>
+          <t>認証</t>
+        </is>
+      </c>
+      <c r="B2" s="13" t="inlineStr">
+        <is>
+          <t>Authorization: Bearer &lt;JWT&gt;（POST /api/auth/login と /actuator/health 以外は必須）。JWT は HS256・有効 2 時間。クレーム: iss=kintaiflow, sub=ユーザーID, role, mcp（要パスワード変更）, iat, exp</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="13" t="inlineStr">
+        <is>
+          <t>認可の多重防御</t>
+        </is>
+      </c>
+      <c r="B3" s="13" t="inlineStr">
+        <is>
+          <t>SecurityConfig で /api/admin/** を ADMIN に限定したうえで各 Controller に @PreAuthorize を付与。API ごとにデータ所有（本人・承認者）を Service で検証する。詳細は権限設計書（KF-BD-004）</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="13" t="inlineStr">
+        <is>
+          <t>認証フィルタ</t>
+        </is>
+      </c>
+      <c r="B4" s="13" t="inlineStr">
+        <is>
+          <t>①ActiveUserFilter: 無効（INACTIVE）・削除済みユーザー、またはパスワード変更・管理者によるパスワード再設定の前に発行されたトークンは 401（E-001）。②PasswordChangeRequiredFilter: mcp=true のトークンは /api/auth/password 以外を 403（E-019）</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="13" t="inlineStr">
+        <is>
+          <t>エラー応答形式</t>
+        </is>
+      </c>
+      <c r="B5" s="13" t="inlineStr">
+        <is>
+          <t>{ "code": "E-0xx", "message": "…", "fieldErrors": [{ "field": "…", "message": "…" }] }。fieldErrors は入力チェック（E-002）のときのみ項目別メッセージを持つ（それ以外は空配列）。Content-Type は application/json;charset=UTF-8</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="13" t="inlineStr">
+        <is>
+          <t>HTTP ステータスとエラーコード</t>
+        </is>
+      </c>
+      <c r="B6" s="13" t="inlineStr">
+        <is>
+          <t>400: E-002, E-003, E-008, E-014, E-018 ／ 401: E-001 ／ 403: E-009, E-010, E-019 ／ 404: E-015 ／ 409: E-004, E-005, E-006, E-007, E-011, E-013, E-016, E-020, E-021, E-022 ／ 423: E-017 ／ 500: E-012。文言は KF-BD-006 メッセージ一覧</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="13" t="inlineStr">
+        <is>
+          <t>入力不正の扱い</t>
+        </is>
+      </c>
+      <c r="B7" s="13" t="inlineStr">
+        <is>
+          <t>JSON 不正・本文欠落・パス/クエリの型不一致・必須クエリ欠落は E-002（400）「入力内容が正しくありません。」。存在しない URL は 404 / E-015</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="13" t="inlineStr">
+        <is>
+          <t>日付・時刻形式</t>
+        </is>
+      </c>
+      <c r="B8" s="13" t="inlineStr">
+        <is>
+          <t>日付 yyyy-MM-dd、月 yyyy-MM、時刻 HH:mm（打刻修正・休憩離席修正の指定）、日時は ISO 8601（+09:00）。業務時刻は Asia/Tokyo（Clock Bean）</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="13" t="inlineStr">
+        <is>
+          <t>CORS・CSRF・セッション</t>
+        </is>
+      </c>
+      <c r="B9" s="13" t="inlineStr">
+        <is>
+          <t>CORS: /api/** に対し許可オリジンを設定値 kintaiflow.cors.allowed-origins で指定（開発は http://localhost:5173）。許可メソッド GET/POST/PUT/DELETE/OPTIONS、許可ヘッダー Authorization / Content-Type。CSRF 無効（トークン方式）・セッションは STATELESS</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="13" t="inlineStr">
+        <is>
+          <t>一覧の件数</t>
+        </is>
+      </c>
+      <c r="B10" s="13" t="inlineStr">
+        <is>
+          <t>申請一覧・承認待ち一覧・ユーザー一覧・集計はページングなしで全件返す。通知一覧のみ最新 50 件</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="landscape"/>
+</worksheet>
 </file>